--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T10:40:39+00:00</t>
+    <t>2024-11-19T13:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T13:31:18+00:00</t>
+    <t>2024-11-19T18:17:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-19T18:17:10+00:00</t>
+    <t>2024-11-20T08:37:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T08:37:30+00:00</t>
+    <t>2024-11-20T15:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T15:15:20+00:00</t>
+    <t>2024-11-22T15:33:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T15:33:20+00:00</t>
+    <t>2024-11-26T16:33:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-26T16:33:37+00:00</t>
+    <t>2024-11-28T11:58:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-28T11:58:57+00:00</t>
+    <t>2024-12-05T16:56:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-05T16:56:49+00:00</t>
+    <t>2024-12-10T08:10:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-10T08:10:26+00:00</t>
+    <t>2024-12-11T08:03:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T08:03:58+00:00</t>
+    <t>2024-12-11T13:32:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T13:32:58+00:00</t>
+    <t>2024-12-11T15:07:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T15:07:35+00:00</t>
+    <t>2024-12-11T17:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T17:05:38+00:00</t>
+    <t>2024-12-12T10:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
+++ b/ig/DM-DECEMBRE-2024/ValueSet-JDV-ModeleDocumentCDA.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-12T10:04:28+00:00</t>
+    <t>2024-12-12T11:26:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
